--- a/docentes/Contreras Díaz Irma Ivette - Estadisticos 20211.xlsx
+++ b/docentes/Contreras Díaz Irma Ivette - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="20">
   <si>
     <t>Mat</t>
   </si>
@@ -77,87 +77,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>COBOS</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>TAMAYO</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>NOLASCO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
-    <t>YOPIHUA</t>
-  </si>
-  <si>
-    <t>HIPOLITO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>GARNICA</t>
-  </si>
-  <si>
-    <t>MIXCOHA</t>
-  </si>
-  <si>
-    <t>YOLET</t>
-  </si>
-  <si>
-    <t>MIGUEL</t>
-  </si>
-  <si>
-    <t>JOSMAR JAHIR</t>
-  </si>
-  <si>
-    <t>ZURY BETZABE</t>
-  </si>
-  <si>
-    <t>PAOLA JAZMIN</t>
-  </si>
-  <si>
-    <t>JOSE JULIAN</t>
-  </si>
-  <si>
-    <t>ALDO GEOVANNI</t>
-  </si>
-  <si>
-    <t>DIEGO DE JESUS</t>
-  </si>
-  <si>
-    <t>CRISTHIAN ALFONSO</t>
   </si>
 </sst>
 </file>
@@ -558,19 +477,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="G2">
-        <v>57.5</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>8.1</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -584,19 +503,19 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="G3">
-        <v>68.18000000000001</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -610,19 +529,19 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G4">
-        <v>81.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -636,19 +555,19 @@
         <v>28</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G5">
-        <v>64.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -662,19 +581,19 @@
         <v>21</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G6">
-        <v>71.43000000000001</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>8.300000000000001</v>
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>
@@ -727,16 +646,19 @@
         <v>40</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>40</v>
       </c>
-      <c r="E2">
-        <v>23</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>7.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -750,16 +672,19 @@
         <v>44</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
         <v>44</v>
       </c>
-      <c r="E3">
-        <v>30</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
       <c r="G3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H3">
+        <v>7.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -773,16 +698,19 @@
         <v>43</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>43</v>
       </c>
-      <c r="E4">
-        <v>35</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>7.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -796,16 +724,19 @@
         <v>28</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
         <v>28</v>
       </c>
-      <c r="E5">
-        <v>18</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H5">
+        <v>7.8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -819,16 +750,19 @@
         <v>21</v>
       </c>
       <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
         <v>21</v>
       </c>
-      <c r="E6">
-        <v>15</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
       <c r="G6">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H6">
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>
@@ -881,19 +815,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="G2">
-        <v>57.5</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -907,19 +841,19 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="G3">
-        <v>68.18000000000001</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -933,16 +867,16 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G4">
-        <v>81.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="H4">
         <v>8.199999999999999</v>
@@ -959,19 +893,19 @@
         <v>28</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G5">
-        <v>64.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>8.699999999999999</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -985,19 +919,19 @@
         <v>21</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G6">
-        <v>71.43000000000001</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1007,7 +941,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1037,213 +971,6 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>21330051920007</v>
-      </c>
-      <c r="B2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920379</v>
-      </c>
-      <c r="B3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920025</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920045</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920185</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" t="s">
-        <v>42</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920092</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" t="s">
-        <v>43</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920098</v>
-      </c>
-      <c r="B8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920115</v>
-      </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" t="s">
-        <v>45</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920139</v>
-      </c>
-      <c r="B10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10">
-        <v>6</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Contreras Díaz Irma Ivette - Estadisticos 20211.xlsx
+++ b/docentes/Contreras Díaz Irma Ivette - Estadisticos 20211.xlsx
@@ -827,7 +827,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -853,7 +853,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -879,7 +879,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -905,7 +905,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>7.9</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8">
